--- a/03_outputs/entrega_final/importancia_variables.xlsx
+++ b/03_outputs/entrega_final/importancia_variables.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="205">
   <si>
     <t>variable</t>
   </si>
@@ -30,6 +30,12 @@
   </si>
   <si>
     <t>02_EN_logit_F1_metrica</t>
+  </si>
+  <si>
+    <t>08_EN_logit_rebalanceo_ROC_importancia</t>
+  </si>
+  <si>
+    <t>08_EN_logit_rebalanceo_ROC_metrica</t>
   </si>
   <si>
     <t>anios_educ_jefe</t>
@@ -966,10 +972,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,2725 +991,3691 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>0.001873407170707988</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1.683988280110321E-08</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>0.2896011221674703</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>0.2896011221674703</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>0.3833352896884358</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>0.00258600153373083</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>0.00258600153373083</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>0.1076391718102291</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>5.08693345802478</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>5.08693345802478</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>5.77326240623335</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>0.009304660995730143</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>0.009304660995730143</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>0.03063838823107963</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>0.8280617726966325</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>0.8280617726966325</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>1.076168126784012</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>0.4276087025140277</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>0.4276087025140277</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>0.5118234655755702</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>0.1453776700380967</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>0.1453776700380967</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>0.18436949516283</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>0.01649322522769299</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>0.0909702832385971</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>0.0909702832385971</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>0.0750708707365885</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>0.2799598663397722</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>0.2799598663397722</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>0.6375754477462099</v>
+      </c>
+      <c r="G19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0.1601355221254885</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>0.1601355221254885</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>0.1534499226963761</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0.2429090070490496</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>0.2429090070490496</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>0.2612601253181444</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F24">
+        <v>0.0460978222897617</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F28">
+        <v>0.01696270104634372</v>
+      </c>
+      <c r="G28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31">
         <v>0.04199246718831294</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>0.04199246718831294</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <v>0.030863166640208</v>
+      </c>
+      <c r="G31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F33">
+        <v>0.04258864476413195</v>
+      </c>
+      <c r="G33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34">
         <v>0.02049813073804792</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>0.02049813073804792</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>0.3479155287476872</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>0.3479155287476872</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>0.1279941633066181</v>
+      </c>
+      <c r="G35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36">
         <v>0.3309613695567352</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>0.3309613695567352</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F36">
+        <v>0.1651571834325328</v>
+      </c>
+      <c r="G36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B37">
         <v>0.4887647418305981</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>0.4887647418305981</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F37">
+        <v>0.3585557341884072</v>
+      </c>
+      <c r="G37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B39">
         <v>0.7215424889167183</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D39">
         <v>0.7215424889167183</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F39">
+        <v>0.974623646446382</v>
+      </c>
+      <c r="G39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40">
         <v>0.1591458631928819</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>0.1591458631928819</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B41">
         <v>3.24352739754324E-09</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>3.24352739754324E-09</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>6.210844936490299E-09</v>
+      </c>
+      <c r="G41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>8.035627024839175E-05</v>
+      </c>
+      <c r="G42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>9.840526629697598E-05</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>9.840526629697598E-05</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F47">
+        <v>0.01164943367337753</v>
+      </c>
+      <c r="G47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B48">
         <v>0.4553800559174459</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D48">
         <v>0.4553800559174459</v>
       </c>
       <c r="E48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F48">
+        <v>0.5450746324806395</v>
+      </c>
+      <c r="G48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F50">
+        <v>0.02142331135211371</v>
+      </c>
+      <c r="G50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52">
         <v>0.4289832866894685</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D52">
         <v>0.4289832866894685</v>
       </c>
       <c r="E52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F52">
+        <v>0.5206511730552055</v>
+      </c>
+      <c r="G52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B57">
         <v>0.2401270168621552</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D57">
         <v>0.2401270168621552</v>
       </c>
       <c r="E57" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F57">
+        <v>0.2608258720224005</v>
+      </c>
+      <c r="G57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B60">
         <v>0.1122552488517007</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D60">
         <v>0.1122552488517007</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F60">
+        <v>0.1372587132602583</v>
+      </c>
+      <c r="G60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B62">
         <v>0.1178433632766242</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D62">
         <v>0.1178433632766242</v>
       </c>
       <c r="E62" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F62">
+        <v>0.2121406919425595</v>
+      </c>
+      <c r="G62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F63">
+        <v>0.03755020243077318</v>
+      </c>
+      <c r="G63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B64">
         <v>0.01217247596215963</v>
       </c>
       <c r="C64" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <v>0.01217247596215963</v>
       </c>
       <c r="E64" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B66">
         <v>0.001737875032339116</v>
       </c>
       <c r="C66" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D66">
         <v>0.001737875032339116</v>
       </c>
       <c r="E66" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F68">
+        <v>0.04555442217154086</v>
+      </c>
+      <c r="G68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B70">
         <v>0.02330773280962162</v>
       </c>
       <c r="C70" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D70">
         <v>0.02330773280962162</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F70">
+        <v>0.01917950415869392</v>
+      </c>
+      <c r="G70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B71">
         <v>0.2235183315444241</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D71">
         <v>0.2235183315444241</v>
       </c>
       <c r="E71" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F71">
+        <v>0.2127108120828664</v>
+      </c>
+      <c r="G71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F72">
+        <v>0.0384356757642761</v>
+      </c>
+      <c r="G72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B73">
         <v>0.04760745293428757</v>
       </c>
       <c r="C73" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D73">
         <v>0.04760745293428757</v>
       </c>
       <c r="E73" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F73">
+        <v>0.08746480546465213</v>
+      </c>
+      <c r="G73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F74">
+        <v>0.07964804661798169</v>
+      </c>
+      <c r="G74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B75">
         <v>0.003805087871868537</v>
       </c>
       <c r="C75" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D75">
         <v>0.003805087871868537</v>
       </c>
       <c r="E75" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F75">
+        <v>0.04139664850116157</v>
+      </c>
+      <c r="G75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B78">
         <v>0.0640206929939591</v>
       </c>
       <c r="C78" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D78">
         <v>0.0640206929939591</v>
       </c>
       <c r="E78" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F78">
+        <v>0.09288308070704747</v>
+      </c>
+      <c r="G78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B79">
         <v>0.1904329768826931</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D79">
         <v>0.1904329768826931</v>
       </c>
       <c r="E79" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F79">
+        <v>0.2598957301201478</v>
+      </c>
+      <c r="G79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B80">
         <v>0.05679467708793034</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D80">
         <v>0.05679467708793034</v>
       </c>
       <c r="E80" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F80">
+        <v>0.04122804835428673</v>
+      </c>
+      <c r="G80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B81">
         <v>0.1482689543005322</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D81">
         <v>0.1482689543005322</v>
       </c>
       <c r="E81" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F81">
+        <v>0.1736011381208021</v>
+      </c>
+      <c r="G81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B82">
         <v>0.04032213195485094</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D82">
         <v>0.04032213195485094</v>
       </c>
       <c r="E82" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F82">
+        <v>0.07195976284732966</v>
+      </c>
+      <c r="G82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B83">
         <v>0.0001298745707567006</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D83">
         <v>0.0001298745707567006</v>
       </c>
       <c r="E83" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B84">
         <v>0.05368363399935151</v>
       </c>
       <c r="C84" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D84">
         <v>0.05368363399935151</v>
       </c>
       <c r="E84" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F84">
+        <v>0.1111577418251776</v>
+      </c>
+      <c r="G84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B86">
         <v>0.03095209562451798</v>
       </c>
       <c r="C86" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D86">
         <v>0.03095209562451798</v>
       </c>
       <c r="E86" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F86">
+        <v>0.03999870390943655</v>
+      </c>
+      <c r="G86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F90">
+        <v>0.001384208311679551</v>
+      </c>
+      <c r="G90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B91">
         <v>0.002764903500694333</v>
       </c>
       <c r="C91" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D91">
         <v>0.002764903500694333</v>
       </c>
       <c r="E91" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F91">
+        <v>0.003974667244018557</v>
+      </c>
+      <c r="G91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B93">
         <v>0.3874889850442119</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D93">
         <v>0.3874889850442119</v>
       </c>
       <c r="E93" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F93">
+        <v>0.4733635671609244</v>
+      </c>
+      <c r="G93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B94">
         <v>0.1553505555849304</v>
       </c>
       <c r="C94" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D94">
         <v>0.1553505555849304</v>
       </c>
       <c r="E94" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F94">
+        <v>0.1415336729781055</v>
+      </c>
+      <c r="G94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B95">
         <v>7.205346948436623E-06</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D95">
         <v>7.205346948436623E-06</v>
       </c>
       <c r="E95" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F95">
+        <v>8.315637048201525E-06</v>
+      </c>
+      <c r="G95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B98">
         <v>0.0787983270633438</v>
       </c>
       <c r="C98" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D98">
         <v>0.0787983270633438</v>
       </c>
       <c r="E98" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F98">
+        <v>0.03525688840358941</v>
+      </c>
+      <c r="G98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B99">
         <v>0.02669926046305193</v>
       </c>
       <c r="C99" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D99">
         <v>0.02669926046305193</v>
       </c>
       <c r="E99" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F99">
+        <v>0.03736863241770132</v>
+      </c>
+      <c r="G99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B104">
         <v>0.1823728144902506</v>
       </c>
       <c r="C104" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D104">
         <v>0.1823728144902506</v>
       </c>
       <c r="E104" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F104">
+        <v>0.1688202776764005</v>
+      </c>
+      <c r="G104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B108">
         <v>0.2250935049582597</v>
       </c>
       <c r="C108" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D108">
         <v>0.2250935049582597</v>
       </c>
       <c r="E108" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F108">
+        <v>0.3229107684325384</v>
+      </c>
+      <c r="G108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F109">
+        <v>0.09992751736056793</v>
+      </c>
+      <c r="G109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B110">
         <v>0.1771102097545652</v>
       </c>
       <c r="C110" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D110">
         <v>0.1771102097545652</v>
       </c>
       <c r="E110" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F110">
+        <v>0.1852802814903722</v>
+      </c>
+      <c r="G110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B113">
         <v>0.05437642624685</v>
       </c>
       <c r="C113" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D113">
         <v>0.05437642624685</v>
       </c>
       <c r="E113" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F113">
+        <v>0.03466324221900014</v>
+      </c>
+      <c r="G113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B116">
         <v>0.03040633999952263</v>
       </c>
       <c r="C116" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D116">
         <v>0.03040633999952263</v>
       </c>
       <c r="E116" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F116">
+        <v>0.03598466430985714</v>
+      </c>
+      <c r="G116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B119">
         <v>1.479621752115486E-06</v>
       </c>
       <c r="C119" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D119">
         <v>1.479621752115486E-06</v>
       </c>
       <c r="E119" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F119">
+        <v>1.499466057593096E-06</v>
+      </c>
+      <c r="G119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B120">
         <v>0.1924561299728316</v>
       </c>
       <c r="C120" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D120">
         <v>0.1924561299728316</v>
       </c>
       <c r="E120" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F120">
+        <v>0.3273996216660961</v>
+      </c>
+      <c r="G120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F122">
+        <v>0.000213456744093135</v>
+      </c>
+      <c r="G122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B123">
         <v>0.0189027198190533</v>
       </c>
       <c r="C123" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D123">
         <v>0.0189027198190533</v>
       </c>
       <c r="E123" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F123">
+        <v>0.004701976918578861</v>
+      </c>
+      <c r="G123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B125">
         <v>0.06458228563529621</v>
       </c>
       <c r="C125" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D125">
         <v>0.06458228563529621</v>
       </c>
       <c r="E125" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F125">
+        <v>0.07878657643563108</v>
+      </c>
+      <c r="G125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B128">
         <v>0.3934041847718908</v>
       </c>
       <c r="C128" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D128">
         <v>0.3934041847718908</v>
       </c>
       <c r="E128" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F128">
+        <v>0.4174688539788465</v>
+      </c>
+      <c r="G128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B130">
         <v>0.6267070114983779</v>
       </c>
       <c r="C130" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D130">
         <v>0.6267070114983779</v>
       </c>
       <c r="E130" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F130">
+        <v>0.7103480428974587</v>
+      </c>
+      <c r="G130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
       <c r="C131" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B134">
         <v>1.326708719543941</v>
       </c>
       <c r="C134" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D134">
         <v>1.326708719543941</v>
       </c>
       <c r="E134" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F134">
+        <v>1.155491855862546</v>
+      </c>
+      <c r="G134" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F135">
+        <v>0.02027714378526736</v>
+      </c>
+      <c r="G135" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B137">
         <v>0.0009119872961052331</v>
       </c>
       <c r="C137" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D137">
         <v>0.0009119872961052331</v>
       </c>
       <c r="E137" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B141">
         <v>0.0003217558476183046</v>
       </c>
       <c r="C141" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D141">
         <v>0.0003217558476183046</v>
       </c>
       <c r="E141" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F141">
+        <v>0.00124082175046854</v>
+      </c>
+      <c r="G141" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B142">
         <v>0.001318762670423954</v>
       </c>
       <c r="C142" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D142">
         <v>0.001318762670423954</v>
       </c>
       <c r="E142" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F142">
+        <v>0.003379499001301928</v>
+      </c>
+      <c r="G142" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B145">
         <v>0.002633298250502361</v>
       </c>
       <c r="C145" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D145">
         <v>0.002633298250502361</v>
       </c>
       <c r="E145" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F145">
+        <v>0.00293053658734779</v>
+      </c>
+      <c r="G145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B148">
         <v>0.0006230473138475309</v>
       </c>
       <c r="C148" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D148">
         <v>0.0006230473138475309</v>
       </c>
       <c r="E148" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F148">
+        <v>0.0005412589165206996</v>
+      </c>
+      <c r="G148" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F149">
+        <v>0.0008883874471679245</v>
+      </c>
+      <c r="G149" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B150">
         <v>0.00163283332242212</v>
       </c>
       <c r="C150" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D150">
         <v>0.00163283332242212</v>
       </c>
       <c r="E150" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F150">
+        <v>0.0006092473131909022</v>
+      </c>
+      <c r="G150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B152">
         <v>0.0002582446556289111</v>
       </c>
       <c r="C152" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D152">
         <v>0.0002582446556289111</v>
       </c>
       <c r="E152" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F152">
+        <v>0.0002974974040893406</v>
+      </c>
+      <c r="G152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D155">
         <v>0</v>
       </c>
       <c r="E155" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B156">
         <v>0.07134448640113064</v>
       </c>
       <c r="C156" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D156">
         <v>0.07134448640113064</v>
       </c>
       <c r="E156" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F156">
+        <v>0.06727366059569828</v>
+      </c>
+      <c r="G156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B157">
         <v>0.01723393010852822</v>
       </c>
       <c r="C157" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D157">
         <v>0.01723393010852822</v>
       </c>
       <c r="E157" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F157">
+        <v>0.000188825712793557</v>
+      </c>
+      <c r="G157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B158">
         <v>0.2022527159468128</v>
       </c>
       <c r="C158" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D158">
         <v>0.2022527159468128</v>
       </c>
       <c r="E158" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F158">
+        <v>0.2389526582824038</v>
+      </c>
+      <c r="G158" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B159">
         <v>0.03090397308388126</v>
       </c>
       <c r="C159" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D159">
         <v>0.03090397308388126</v>
       </c>
       <c r="E159" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F159">
+        <v>0.01644214194608841</v>
+      </c>
+      <c r="G159" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
       <c r="C160" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D160">
         <v>0</v>
       </c>
       <c r="E160" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
       <c r="C161" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D161">
         <v>0</v>
       </c>
       <c r="E161" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+      <c r="G161" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3718,13 +4690,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3732,10 +4704,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3743,10 +4715,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3754,10 +4726,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3765,10 +4737,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3776,10 +4748,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" t="s">
         <v>174</v>
-      </c>
-      <c r="C6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3787,10 +4759,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3798,10 +4770,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3809,7 +4781,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>179</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3817,7 +4792,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3825,7 +4800,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3833,7 +4808,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3841,7 +4816,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3849,7 +4824,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3857,7 +4832,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3865,7 +4840,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3873,7 +4848,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3881,7 +4856,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3889,7 +4864,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3897,7 +4872,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3905,7 +4880,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3913,7 +4888,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3921,7 +4896,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3929,7 +4904,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3937,7 +4912,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3945,7 +4920,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3953,7 +4928,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3961,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3969,7 +4944,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3977,7 +4952,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3985,7 +4960,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3993,7 +4968,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4001,7 +4976,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4009,7 +4984,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
